--- a/data/trans_camb/P16A01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A01-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 5,73</t>
+          <t>-1,41; 5,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,31</t>
+          <t>-4,39; 2,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 2,71</t>
+          <t>-6,06; 2,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 9,38</t>
+          <t>1,92; 9,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 9,25</t>
+          <t>1,35; 8,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 7,18</t>
+          <t>-2,55; 7,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,44</t>
+          <t>0,96; 6,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,43</t>
+          <t>-0,55; 4,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,95</t>
+          <t>-3,47; 3,05</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 105,12</t>
+          <t>-17,14; 101,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,19; 39,83</t>
+          <t>-51,56; 45,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-75,7; 48,41</t>
+          <t>-74,48; 53,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,07; 193,21</t>
+          <t>21,78; 195,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 183,18</t>
+          <t>15,28; 180,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 142,12</t>
+          <t>-36,76; 145,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,03; 111,75</t>
+          <t>11,86; 104,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 72,71</t>
+          <t>-6,8; 80,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,94; 51,23</t>
+          <t>-45,45; 52,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,6</t>
+          <t>2,04; 7,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,16</t>
+          <t>1,36; 7,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 11,24</t>
+          <t>2,7; 11,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 4,75</t>
+          <t>-1,74; 4,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,62</t>
+          <t>-2,24; 3,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 3,16</t>
+          <t>-4,29; 3,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,44</t>
+          <t>1,21; 5,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,66</t>
+          <t>0,43; 4,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,66</t>
+          <t>-0,26; 5,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,22; 210,9</t>
+          <t>31,54; 206,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,57; 202,11</t>
+          <t>19,54; 180,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,19; 296,73</t>
+          <t>37,97; 295,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 79,64</t>
+          <t>-19,67; 81,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 60,92</t>
+          <t>-24,9; 69,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,42; 50,38</t>
+          <t>-48,85; 45,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,39; 102,96</t>
+          <t>16,62; 107,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 92,52</t>
+          <t>4,81; 90,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 103,99</t>
+          <t>-3,81; 107,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,46</t>
+          <t>-0,48; 5,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 3,89</t>
+          <t>-1,75; 3,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,65</t>
+          <t>-1,6; 4,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,64</t>
+          <t>-3,29; 2,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 3,53</t>
+          <t>-2,49; 3,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,99</t>
+          <t>-3,4; 1,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,92</t>
+          <t>-1,21; 3,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,81</t>
+          <t>-1,15; 2,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,36</t>
+          <t>-1,79; 2,32</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 105,13</t>
+          <t>-8,0; 111,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 82,11</t>
+          <t>-22,84; 76,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 99,42</t>
+          <t>-20,74; 96,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 44,43</t>
+          <t>-34,13; 45,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,76; 57,34</t>
+          <t>-28,07; 55,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 34,51</t>
+          <t>-38,16; 32,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 48,23</t>
+          <t>-15,18; 51,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 48,37</t>
+          <t>-14,72; 48,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 40,79</t>
+          <t>-22,93; 39,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 5,7</t>
+          <t>-0,43; 5,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 4,11</t>
+          <t>-1,73; 4,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 2,72</t>
+          <t>-4,5; 2,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,24</t>
+          <t>0,37; 6,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,34</t>
+          <t>0,08; 5,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,35</t>
+          <t>-0,4; 4,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,07</t>
+          <t>0,89; 5,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,85</t>
+          <t>-0,05; 3,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,66</t>
+          <t>-1,94; 2,68</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 158,89</t>
+          <t>-11,02; 155,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,02; 109,78</t>
+          <t>-27,45; 116,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,27; 64,08</t>
+          <t>-63,5; 63,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 210,24</t>
+          <t>4,51; 208,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 193,66</t>
+          <t>0,18; 182,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 146,75</t>
+          <t>-8,8; 147,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,41; 141,28</t>
+          <t>13,35; 142,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 109,07</t>
+          <t>-1,29; 106,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 68,34</t>
+          <t>-31,06; 69,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 6,57</t>
+          <t>-1,24; 6,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 4,21</t>
+          <t>-2,58; 4,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,96</t>
+          <t>-4,45; 1,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,76</t>
+          <t>-2,21; 4,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 6,23</t>
+          <t>-0,12; 6,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,29</t>
+          <t>0,68; 6,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,24</t>
+          <t>-0,83; 3,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,48</t>
+          <t>-0,46; 4,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,45</t>
+          <t>-0,75; 3,33</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 131,97</t>
+          <t>-14,44; 131,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,82; 86,08</t>
+          <t>-29,64; 97,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-48,15; 41,37</t>
+          <t>-47,17; 38,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,77; 101,75</t>
+          <t>-33,57; 104,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 164,63</t>
+          <t>-3,48; 178,23</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,62; 166,74</t>
+          <t>4,87; 172,53</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 86,88</t>
+          <t>-13,07; 80,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 91,43</t>
+          <t>-7,91; 98,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 73,77</t>
+          <t>-10,09; 68,8</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 5,3</t>
+          <t>-4,51; 5,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 2,08</t>
+          <t>-6,89; 2,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 1,75</t>
+          <t>-6,45; 1,84</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 2,73</t>
+          <t>-5,21; 3,16</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 2,92</t>
+          <t>-4,65; 3,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 0,58</t>
+          <t>-8,52; 0,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,8</t>
+          <t>-3,64; 2,54</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 1,49</t>
+          <t>-4,62; 1,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 0,06</t>
+          <t>-7,43; 0,27</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-35,52; 68,72</t>
+          <t>-36,81; 64,58</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-55,75; 30,32</t>
+          <t>-55,28; 29,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 24,17</t>
+          <t>-49,36; 24,99</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-48,19; 43,36</t>
+          <t>-50,54; 50,69</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-48,37; 49,57</t>
+          <t>-47,21; 50,72</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,57; 7,81</t>
+          <t>-76,85; 1,76</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 35,32</t>
+          <t>-33,72; 34,34</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-41,69; 20,48</t>
+          <t>-42,98; 18,28</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-63,28; -0,79</t>
+          <t>-68,26; 2,99</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 5,39</t>
+          <t>-8,14; 5,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 1,74</t>
+          <t>-11,65; 1,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -6,16</t>
+          <t>-17,68; -6,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,22</t>
+          <t>0,46; 8,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,45; 8,78</t>
+          <t>-0,39; 8,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,93</t>
+          <t>0,41; 6,77</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,0</t>
+          <t>-1,08; 6,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,65</t>
+          <t>-2,59; 4,56</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,99</t>
+          <t>-4,56; 0,99</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-42,0; 41,8</t>
+          <t>-40,86; 42,97</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-51,24; 13,36</t>
+          <t>-53,99; 10,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-78,92; -44,94</t>
+          <t>-79,98; -44,91</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,89; 261,26</t>
+          <t>3,12; 263,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,64; 280,43</t>
+          <t>-8,03; 263,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,64; 257,36</t>
+          <t>2,63; 218,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 79,42</t>
+          <t>-12,3; 84,94</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 63,96</t>
+          <t>-23,29; 60,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,7; 13,48</t>
+          <t>-39,49; 13,75</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,97</t>
+          <t>1,16; 3,85</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,22</t>
+          <t>-0,63; 2,02</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,11</t>
+          <t>-1,98; 1,09</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,29</t>
+          <t>0,64; 3,18</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,18</t>
+          <t>0,65; 3,37</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,04</t>
+          <t>-0,72; 1,91</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,08</t>
+          <t>1,28; 3,1</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,22</t>
+          <t>0,4; 2,35</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,33</t>
+          <t>-0,75; 1,31</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>15,76; 61,9</t>
+          <t>15,9; 61,55</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 36,0</t>
+          <t>-7,9; 32,24</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 17,16</t>
+          <t>-27,16; 16,71</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9,78; 56,37</t>
+          <t>8,64; 53,27</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,59; 54,88</t>
+          <t>9,37; 58,99</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 34,57</t>
+          <t>-10,29; 31,79</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,82; 48,01</t>
+          <t>17,66; 50,05</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>6,53; 35,43</t>
+          <t>5,51; 37,07</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 21,44</t>
+          <t>-10,58; 20,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A01-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A01-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 5,62</t>
+          <t>-1,46; 5,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,45</t>
+          <t>-4,29; 2,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 2,89</t>
+          <t>-5,32; 3,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,24</t>
+          <t>1,94; 9,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,99</t>
+          <t>1,49; 8,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 7,48</t>
+          <t>-2,46; 7,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 6,12</t>
+          <t>1,32; 6,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,51</t>
+          <t>-0,51; 4,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 3,05</t>
+          <t>-2,73; 3,49</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-32,94%</t>
+          <t>-16,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-8,57%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 101,56</t>
+          <t>-18,01; 94,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 45,9</t>
+          <t>-51,52; 41,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,48; 53,44</t>
+          <t>-66,63; 58,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,78; 195,01</t>
+          <t>17,99; 182,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,28; 180,26</t>
+          <t>18,4; 187,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,76; 145,82</t>
+          <t>-33,79; 136,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,86; 104,35</t>
+          <t>16,0; 107,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 80,24</t>
+          <t>-6,28; 79,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,45; 52,36</t>
+          <t>-35,69; 58,04</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,59</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>3,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,64</t>
+          <t>2,18; 7,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,14</t>
+          <t>1,04; 6,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 11,5</t>
+          <t>2,0; 10,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 4,84</t>
+          <t>-1,42; 5,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,94</t>
+          <t>-2,11; 3,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 3,22</t>
+          <t>-3,55; 3,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,6</t>
+          <t>1,12; 5,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,73</t>
+          <t>0,33; 4,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,66</t>
+          <t>0,62; 5,88</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140,87%</t>
+          <t>135,52%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-8,14%</t>
+          <t>-3,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,54; 206,88</t>
+          <t>36,88; 222,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,54; 180,87</t>
+          <t>16,99; 181,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,97; 295,92</t>
+          <t>29,68; 287,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 81,94</t>
+          <t>-14,92; 88,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 69,07</t>
+          <t>-24,15; 64,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,85; 45,81</t>
+          <t>-38,08; 55,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,62; 107,43</t>
+          <t>15,91; 106,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 90,91</t>
+          <t>3,0; 94,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 107,37</t>
+          <t>8,75; 110,46</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,28</t>
+          <t>-0,79; 5,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,85</t>
+          <t>-1,42; 4,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 4,64</t>
+          <t>-1,48; 4,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 2,68</t>
+          <t>-3,4; 2,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,39</t>
+          <t>-2,58; 3,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,9</t>
+          <t>-3,4; 2,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,05</t>
+          <t>-0,96; 3,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,78</t>
+          <t>-1,23; 2,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,32</t>
+          <t>-2,06; 2,1</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-9,6%</t>
+          <t>-10,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 111,12</t>
+          <t>-11,46; 109,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 76,67</t>
+          <t>-19,06; 93,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 96,62</t>
+          <t>-19,95; 94,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 45,07</t>
+          <t>-36,44; 43,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 55,93</t>
+          <t>-28,88; 58,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,16; 32,87</t>
+          <t>-38,86; 38,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 51,47</t>
+          <t>-11,1; 57,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 48,28</t>
+          <t>-16,02; 50,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 39,87</t>
+          <t>-25,58; 36,3</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>1,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 5,98</t>
+          <t>-0,52; 5,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 4,16</t>
+          <t>-1,8; 4,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,83</t>
+          <t>-1,42; 4,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 6,2</t>
+          <t>0,47; 6,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,59</t>
+          <t>0,18; 5,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,21</t>
+          <t>0,03; 4,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,29</t>
+          <t>0,78; 5,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,89</t>
+          <t>-0,15; 3,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,68</t>
+          <t>0,05; 3,74</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-7,87%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 155,0</t>
+          <t>-8,98; 150,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,45; 116,68</t>
+          <t>-28,2; 114,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,5; 63,66</t>
+          <t>-22,21; 112,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 208,34</t>
+          <t>5,04; 201,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 182,26</t>
+          <t>1,92; 184,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 147,12</t>
+          <t>-1,48; 150,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,35; 142,12</t>
+          <t>11,68; 131,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 106,98</t>
+          <t>-3,35; 104,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 69,81</t>
+          <t>-0,1; 103,45</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,38</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 6,41</t>
+          <t>-1,44; 6,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 4,5</t>
+          <t>-2,82; 4,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 1,96</t>
+          <t>-4,19; 1,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 4,2</t>
+          <t>-2,34; 3,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 6,65</t>
+          <t>-0,38; 6,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,54</t>
+          <t>0,88; 6,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,99</t>
+          <t>-0,74; 4,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,79</t>
+          <t>-0,47; 4,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,33</t>
+          <t>-0,9; 3,37</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-13,73%</t>
+          <t>-15,87%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 131,34</t>
+          <t>-18,09; 125,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 97,01</t>
+          <t>-32,96; 95,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 38,34</t>
+          <t>-47,41; 38,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 104,17</t>
+          <t>-35,44; 105,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 178,23</t>
+          <t>-7,65; 173,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,87; 172,53</t>
+          <t>12,02; 180,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 80,98</t>
+          <t>-11,49; 92,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 98,6</t>
+          <t>-6,18; 94,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 68,8</t>
+          <t>-11,66; 70,69</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-1,92</t>
+          <t>-2,06</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,26</t>
+          <t>-0,4</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,88</t>
+          <t>-1,17</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 5,41</t>
+          <t>-5,08; 5,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 2,19</t>
+          <t>-7,37; 1,65</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 1,84</t>
+          <t>-6,58; 1,77</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 3,16</t>
+          <t>-5,4; 2,78</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,12</t>
+          <t>-4,88; 3,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 0,36</t>
+          <t>-4,47; 2,75</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,54</t>
+          <t>-3,83; 2,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 1,36</t>
+          <t>-4,86; 1,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 0,27</t>
+          <t>-3,91; 1,24</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-19,16%</t>
+          <t>-20,52%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-38,3%</t>
+          <t>-4,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-31,29%</t>
+          <t>-12,67%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 64,58</t>
+          <t>-40,7; 71,98</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-55,28; 29,41</t>
+          <t>-56,53; 22,73</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 24,99</t>
+          <t>-50,81; 25,77</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-50,54; 50,69</t>
+          <t>-51,81; 47,25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 50,72</t>
+          <t>-46,58; 48,82</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-76,85; 1,76</t>
+          <t>-38,24; 43,41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,72; 34,34</t>
+          <t>-35,72; 31,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 18,28</t>
+          <t>-42,62; 16,12</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-68,26; 2,99</t>
+          <t>-35,06; 17,51</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-11,02</t>
+          <t>-11,13</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,84</t>
+          <t>-1,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 5,8</t>
+          <t>-7,5; 6,29</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 1,21</t>
+          <t>-10,98; 1,51</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,68; -6,02</t>
+          <t>-17,6; -6,21</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,46; 8,34</t>
+          <t>0,85; 8,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 8,2</t>
+          <t>0,47; 8,6</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,77</t>
+          <t>0,47; 7,01</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 6,24</t>
+          <t>-1,3; 6,11</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 4,56</t>
+          <t>-2,75; 4,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,99</t>
+          <t>-4,99; 0,94</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-65,58%</t>
+          <t>-66,26%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-19,46%</t>
+          <t>-20,21%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 42,97</t>
+          <t>-38,61; 48,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-53,99; 10,79</t>
+          <t>-53,1; 11,24</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-79,98; -44,91</t>
+          <t>-79,94; -45,78</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3,12; 263,19</t>
+          <t>7,34; 276,7</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 263,59</t>
+          <t>1,22; 269,62</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,63; 218,16</t>
+          <t>2,26; 269,59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 84,94</t>
+          <t>-13,02; 80,96</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 60,31</t>
+          <t>-24,2; 58,12</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-39,49; 13,75</t>
+          <t>-41,88; 12,72</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,85</t>
+          <t>1,09; 3,9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,02</t>
+          <t>-0,53; 2,15</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,09</t>
+          <t>-1,04; 1,67</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,18</t>
+          <t>0,5; 3,2</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,37</t>
+          <t>0,62; 3,27</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,91</t>
+          <t>0,07; 2,47</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,1</t>
+          <t>1,27; 3,09</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,35</t>
+          <t>0,48; 2,24</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,31</t>
+          <t>-0,06; 1,67</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-4,5%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>15,9; 61,55</t>
+          <t>14,49; 62,05</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 32,24</t>
+          <t>-7,15; 33,99</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 16,71</t>
+          <t>-14,12; 26,72</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,64; 53,27</t>
+          <t>7,16; 54,85</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,37; 58,99</t>
+          <t>8,7; 56,66</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 31,79</t>
+          <t>1,3; 44,14</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,66; 50,05</t>
+          <t>17,75; 49,18</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>5,51; 37,07</t>
+          <t>6,72; 35,94</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 20,97</t>
+          <t>-0,77; 26,99</t>
         </is>
       </c>
     </row>
